--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484040_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484040_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.7858</v>
+        <v>2.0637</v>
       </c>
       <c r="E2" t="n">
-        <v>1.7907</v>
+        <v>1.4052</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9951</v>
+        <v>0.6584</v>
       </c>
       <c r="G2" t="n">
         <v>-0.1574</v>
@@ -610,13 +610,13 @@
         <v>1.9838</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9432</v>
+        <v>0.221</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5613</v>
+        <v>0.1758</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3819</v>
+        <v>0.0452</v>
       </c>
       <c r="V2" t="n">
         <v>1.2065</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.6516999999999999</v>
+        <v>-0.6237</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.6516999999999999</v>
+        <v>-0.6237</v>
       </c>
       <c r="G3" t="n">
         <v>-0.7328</v>
@@ -688,13 +688,13 @@
         <v>0.1984</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1173</v>
+        <v>-0.0893</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1173</v>
+        <v>-0.0893</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. ROYO SANTOS</t>
+          <t>M. SMITH</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.6436</v>
+        <v>-1.4183</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.9919</v>
+        <v>-0.8183</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.6516999999999999</v>
+        <v>-0.6</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.7328</v>
+        <v>2.5358</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.06560000000000001</v>
+        <v>1.5926</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.6672</v>
+        <v>0.9432</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>2.7525</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>2.1074</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>0.6451</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.7328</v>
+        <v>-0.2168</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.06560000000000001</v>
+        <v>-0.5148</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.6672</v>
+        <v>0.2981</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.7935</v>
+        <v>-1.3887</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9919</v>
+        <v>-2.9758</v>
       </c>
       <c r="R4" t="n">
-        <v>0.1984</v>
+        <v>1.5871</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1173</v>
+        <v>-1.3589</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>-0.595</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1173</v>
+        <v>-0.7639</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-1.2065</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. SMITH</t>
+          <t>J. ROYO SANTOS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.868</v>
+        <v>-1.6156</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.9033</v>
+        <v>-0.9919</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.9647</v>
+        <v>-0.6237</v>
       </c>
       <c r="G5" t="n">
-        <v>2.5358</v>
+        <v>-0.7328</v>
       </c>
       <c r="H5" t="n">
-        <v>1.5926</v>
+        <v>-0.06560000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9432</v>
+        <v>-0.6672</v>
       </c>
       <c r="J5" t="n">
-        <v>2.7525</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>2.1074</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6451</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2168</v>
+        <v>-0.7328</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5148</v>
+        <v>-0.06560000000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2981</v>
+        <v>-0.6672</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.3887</v>
+        <v>-0.7935</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.9758</v>
+        <v>-0.9919</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5871</v>
+        <v>0.1984</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.8086</v>
+        <v>-0.0893</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.68</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.1286</v>
+        <v>-0.0893</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.2065</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2065</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.3952</v>
+        <v>-2.2807</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.1277</v>
+        <v>-0.901</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.2674</v>
+        <v>-1.3797</v>
       </c>
       <c r="G6" t="n">
         <v>0.1133</v>
@@ -922,13 +922,13 @@
         <v>0.9919</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9647</v>
+        <v>-0.8502</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4874</v>
+        <v>-0.2607</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4773</v>
+        <v>-0.5896</v>
       </c>
       <c r="V6" t="n">
         <v>-1.5437</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.8083</v>
+        <v>-2.6009</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.0501</v>
+        <v>-1.0671</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.7583</v>
+        <v>-1.5338</v>
       </c>
       <c r="G7" t="n">
         <v>-1.6046</v>
@@ -1000,13 +1000,13 @@
         <v>2.579</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.12</v>
+        <v>-0.9126</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2323</v>
+        <v>-0.2493</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.8877</v>
+        <v>-0.6632</v>
       </c>
       <c r="V7" t="n">
         <v>-1.4724</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.3234</v>
+        <v>-2.8646</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.2856</v>
+        <v>-0.8548</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.0378</v>
+        <v>-2.0098</v>
       </c>
       <c r="G8" t="n">
         <v>-3.0061</v>
@@ -1078,13 +1078,13 @@
         <v>2.1822</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6898</v>
+        <v>-0.231</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7368</v>
+        <v>-0.306</v>
       </c>
       <c r="U8" t="n">
-        <v>0.047</v>
+        <v>0.0751</v>
       </c>
       <c r="V8" t="n">
         <v>-1.8097</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.9019</v>
+        <v>-3.6587</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.9415</v>
+        <v>-2.7545</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.9604</v>
+        <v>-0.9043</v>
       </c>
       <c r="G9" t="n">
         <v>-2.6579</v>
@@ -1156,13 +1156,13 @@
         <v>1.9838</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.9942</v>
+        <v>-0.751</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4817</v>
+        <v>-0.2946</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5125</v>
+        <v>-0.4564</v>
       </c>
       <c r="V9" t="n">
         <v>0.9405</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.3468</v>
+        <v>-4.0359</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.5224</v>
+        <v>-3.2957</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8244</v>
+        <v>-0.7402</v>
       </c>
       <c r="G10" t="n">
         <v>-0.6236</v>
@@ -1234,13 +1234,13 @@
         <v>0.9919</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.2589</v>
+        <v>-0.948</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5611</v>
+        <v>-0.3344</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6978</v>
+        <v>-0.6136</v>
       </c>
       <c r="V10" t="n">
         <v>-1.4724</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.4658</v>
+        <v>-4.1116</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.5049</v>
+        <v>-2.87</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.961</v>
+        <v>-1.2415</v>
       </c>
       <c r="G11" t="n">
         <v>-1.4974</v>
@@ -1312,13 +1312,13 @@
         <v>1.9838</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3571</v>
+        <v>-0.0028</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7991</v>
+        <v>-0.1643</v>
       </c>
       <c r="U11" t="n">
-        <v>0.442</v>
+        <v>0.1615</v>
       </c>
       <c r="V11" t="n">
         <v>-2.4129</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.2936</v>
+        <v>-7.5195</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.5631</v>
+        <v>-6.7048</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.7305</v>
+        <v>-0.8146</v>
       </c>
       <c r="G12" t="n">
         <v>-2.3978</v>
@@ -1390,13 +1390,13 @@
         <v>2.1822</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2783</v>
+        <v>0.0524</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1304</v>
+        <v>-0.0113</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1479</v>
+        <v>0.06370000000000001</v>
       </c>
       <c r="V12" t="n">
         <v>-1.2065</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-29.91249999999999</v>
+        <v>-28.6658</v>
       </c>
       <c r="E13" t="n">
-        <v>-20.0998</v>
+        <v>-18.8529</v>
       </c>
       <c r="F13" t="n">
-        <v>-9.812799999999999</v>
+        <v>-9.812900000000001</v>
       </c>
       <c r="G13" t="n">
         <v>-10.7613</v>
@@ -1468,13 +1468,13 @@
         <v>16.8625</v>
       </c>
       <c r="S13" t="n">
-        <v>-6.206399999999999</v>
+        <v>-4.9597</v>
       </c>
       <c r="T13" t="n">
-        <v>-3.286700000000001</v>
+        <v>-2.0398</v>
       </c>
       <c r="U13" t="n">
-        <v>-2.9197</v>
+        <v>-2.9198</v>
       </c>
       <c r="V13" t="n">
         <v>-8.9771</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>9.291499999999999</v>
+        <v>9.437799999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>3.8797</v>
+        <v>3.7776</v>
       </c>
       <c r="F14" t="n">
-        <v>5.4119</v>
+        <v>5.6601</v>
       </c>
       <c r="G14" t="n">
         <v>3.8228</v>
@@ -1546,13 +1546,13 @@
         <v>3.7693</v>
       </c>
       <c r="S14" t="n">
-        <v>1.4012</v>
+        <v>1.5474</v>
       </c>
       <c r="T14" t="n">
-        <v>0.8843</v>
+        <v>0.7823</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5168</v>
+        <v>0.7651</v>
       </c>
       <c r="V14" t="n">
         <v>2.6789</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.4089</v>
+        <v>6.5357</v>
       </c>
       <c r="E15" t="n">
-        <v>2.39</v>
+        <v>1.7779</v>
       </c>
       <c r="F15" t="n">
-        <v>5.0189</v>
+        <v>4.7579</v>
       </c>
       <c r="G15" t="n">
         <v>2.1683</v>
@@ -1624,13 +1624,13 @@
         <v>3.7693</v>
       </c>
       <c r="S15" t="n">
-        <v>2.8357</v>
+        <v>1.9626</v>
       </c>
       <c r="T15" t="n">
-        <v>1.5645</v>
+        <v>0.9523</v>
       </c>
       <c r="U15" t="n">
-        <v>1.2712</v>
+        <v>1.0102</v>
       </c>
       <c r="V15" t="n">
         <v>1.8097</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.3982</v>
+        <v>5.5861</v>
       </c>
       <c r="E16" t="n">
         <v>2.9448</v>
       </c>
       <c r="F16" t="n">
-        <v>2.4534</v>
+        <v>2.6413</v>
       </c>
       <c r="G16" t="n">
         <v>0.8048999999999999</v>
@@ -1702,13 +1702,13 @@
         <v>2.579</v>
       </c>
       <c r="S16" t="n">
-        <v>1.3949</v>
+        <v>1.5828</v>
       </c>
       <c r="T16" t="n">
         <v>0.6236</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7713</v>
+        <v>0.9592000000000001</v>
       </c>
       <c r="V16" t="n">
         <v>1.8097</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.5816</v>
+        <v>4.8716</v>
       </c>
       <c r="E17" t="n">
-        <v>3.1157</v>
+        <v>3.2177</v>
       </c>
       <c r="F17" t="n">
-        <v>1.4659</v>
+        <v>1.6538</v>
       </c>
       <c r="G17" t="n">
         <v>0.4782</v>
@@ -1780,13 +1780,13 @@
         <v>2.579</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5163</v>
+        <v>0.8063</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3288</v>
+        <v>0.4309</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1875</v>
+        <v>0.3754</v>
       </c>
       <c r="V17" t="n">
         <v>1.2065</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>4.0037</v>
+        <v>4.6822</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6022</v>
+        <v>1.1124</v>
       </c>
       <c r="F18" t="n">
-        <v>3.4015</v>
+        <v>3.5698</v>
       </c>
       <c r="G18" t="n">
         <v>3.1206</v>
@@ -1858,13 +1858,13 @@
         <v>2.579</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5056</v>
+        <v>0.1728</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6121</v>
+        <v>-0.102</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1065</v>
+        <v>0.2748</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>3.5636</v>
+        <v>3.7557</v>
       </c>
       <c r="E19" t="n">
         <v>1.5155</v>
       </c>
       <c r="F19" t="n">
-        <v>2.0481</v>
+        <v>2.2402</v>
       </c>
       <c r="G19" t="n">
         <v>0.4719</v>
@@ -1936,13 +1936,13 @@
         <v>2.579</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2981</v>
+        <v>0.4903</v>
       </c>
       <c r="T19" t="n">
         <v>0.1191</v>
       </c>
       <c r="U19" t="n">
-        <v>0.179</v>
+        <v>0.3712</v>
       </c>
       <c r="V19" t="n">
         <v>1.2065</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0124</v>
+        <v>0.3287</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.1006</v>
+        <v>0.1034</v>
       </c>
       <c r="F20" t="n">
-        <v>0.113</v>
+        <v>0.2252</v>
       </c>
       <c r="G20" t="n">
         <v>1.4</v>
@@ -2014,13 +2014,13 @@
         <v>1.1903</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3956</v>
+        <v>-0.0794</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3627</v>
+        <v>-0.1587</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0329</v>
+        <v>0.0793</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4052</v>
+        <v>-0.997</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.4221</v>
+        <v>-1.2383</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0169</v>
+        <v>0.2414</v>
       </c>
       <c r="G21" t="n">
         <v>-2.8662</v>
@@ -2092,13 +2092,13 @@
         <v>0.3968</v>
       </c>
       <c r="S21" t="n">
-        <v>0.7902</v>
+        <v>0.1984</v>
       </c>
       <c r="T21" t="n">
-        <v>0.924</v>
+        <v>0.1077</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1338</v>
+        <v>0.0906</v>
       </c>
       <c r="V21" t="n">
         <v>1.4724</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.2541</v>
+        <v>-1.1241</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.9336</v>
+        <v>-0.8316</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.3205</v>
+        <v>-0.2925</v>
       </c>
       <c r="G22" t="n">
         <v>0.3927</v>
@@ -2170,13 +2170,13 @@
         <v>0.5952</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0436</v>
+        <v>0.0864</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0623</v>
+        <v>0.0397</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0187</v>
+        <v>0.0468</v>
       </c>
       <c r="V22" t="n">
         <v>-1.2065</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.688</v>
+        <v>-1.8037</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.1788</v>
+        <v>-2.5666</v>
       </c>
       <c r="F23" t="n">
-        <v>0.4908</v>
+        <v>0.7629</v>
       </c>
       <c r="G23" t="n">
         <v>0.968</v>
@@ -2248,13 +2248,13 @@
         <v>0.7935</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.08500000000000001</v>
+        <v>0.7992</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4874</v>
+        <v>0.1248</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4024</v>
+        <v>0.6744</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>29.9126</v>
+        <v>31.273</v>
       </c>
       <c r="E24" t="n">
         <v>9.812799999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>20.0999</v>
+        <v>21.4601</v>
       </c>
       <c r="G24" t="n">
         <v>10.7612</v>
@@ -2326,13 +2326,13 @@
         <v>20.8304</v>
       </c>
       <c r="S24" t="n">
-        <v>6.206600000000001</v>
+        <v>7.5668</v>
       </c>
       <c r="T24" t="n">
-        <v>2.9198</v>
+        <v>2.9197</v>
       </c>
       <c r="U24" t="n">
-        <v>3.2867</v>
+        <v>4.647</v>
       </c>
       <c r="V24" t="n">
         <v>8.977199999999998</v>
